--- a/test-automation/EN301549v4.1.1-automation-matrix.en.xlsx
+++ b/test-automation/EN301549v4.1.1-automation-matrix.en.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\a11y-best-practices\test-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743C128A-B648-466A-A525-A72C1D10C80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3D2794-F183-4BBF-B234-041209D3FC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5115" yWindow="-21600" windowWidth="26010" windowHeight="21705" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foreword" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">iOS!$A$1:$B$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Web!$A$1:$C$168</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -399,7 +399,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="405">
   <si>
     <t>shall</t>
   </si>
@@ -838,9 +838,6 @@
 Frankenfeld (2026)</t>
   </si>
   <si>
-    <t>Team</t>
-  </si>
-  <si>
     <t>Kopp (2025)</t>
   </si>
   <si>
@@ -1611,6 +1608,15 @@
   </si>
   <si>
     <t>manual (only presence)</t>
+  </si>
+  <si>
+    <t>Team A</t>
+  </si>
+  <si>
+    <t>Dream Team</t>
+  </si>
+  <si>
+    <t>Serhat</t>
   </si>
 </sst>
 </file>
@@ -1915,7 +1921,7 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2115,13 +2121,12 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2130,7 +2135,29 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7" tint="0.59996337778862885"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7" tint="0.59996337778862885"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -2208,6 +2235,28 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7" tint="0.59996337778862885"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7" tint="0.59996337778862885"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2552,7 +2601,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>139</v>
       </c>
@@ -2583,43 +2632,43 @@
   <sheetData>
     <row r="1" spans="1:142" s="9" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="58" t="s">
+        <v>239</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="E1" s="58" t="s">
-        <v>240</v>
-      </c>
-      <c r="F1" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>166</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>167</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="K1" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="L1" s="53" t="s">
         <v>230</v>
       </c>
-      <c r="L1" s="53" t="s">
+      <c r="M1" s="53" t="s">
         <v>231</v>
-      </c>
-      <c r="M1" s="53" t="s">
-        <v>232</v>
       </c>
       <c r="N1" s="53"/>
       <c r="O1" s="53"/>
@@ -2759,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E2" s="60"/>
       <c r="F2" s="60"/>
@@ -2773,10 +2822,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E3" s="60"/>
       <c r="F3" s="60"/>
@@ -2788,7 +2837,7 @@
       <c r="B4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="90"/>
+      <c r="D4" s="89"/>
       <c r="E4" s="60"/>
       <c r="F4" s="60"/>
     </row>
@@ -2799,7 +2848,6 @@
       <c r="B5" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="91"/>
       <c r="E5" s="60"/>
       <c r="F5" s="60"/>
     </row>
@@ -2810,7 +2858,6 @@
       <c r="B6" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="91"/>
       <c r="E6" s="60"/>
       <c r="F6" s="60"/>
     </row>
@@ -2821,7 +2868,6 @@
       <c r="B7" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="91"/>
       <c r="E7" s="60"/>
       <c r="F7" s="60"/>
     </row>
@@ -2832,7 +2878,6 @@
       <c r="B8" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="91"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
     </row>
@@ -2843,7 +2888,6 @@
       <c r="B9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="91"/>
       <c r="E9" s="60"/>
       <c r="F9" s="60"/>
     </row>
@@ -2854,7 +2898,7 @@
       <c r="B10" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="90"/>
+      <c r="D10" s="89"/>
       <c r="E10" s="60"/>
       <c r="F10" s="60"/>
     </row>
@@ -2865,7 +2909,7 @@
       <c r="B11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="90"/>
+      <c r="D11" s="89"/>
       <c r="E11" s="60"/>
       <c r="F11" s="60"/>
     </row>
@@ -2876,7 +2920,7 @@
       <c r="B12" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="90"/>
+      <c r="D12" s="89"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
     </row>
@@ -2887,7 +2931,7 @@
       <c r="B13" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="90"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="60"/>
       <c r="F13" s="60"/>
     </row>
@@ -2898,7 +2942,7 @@
       <c r="B14" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="90"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="60"/>
       <c r="F14" s="60"/>
     </row>
@@ -2909,7 +2953,6 @@
       <c r="B15" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D15" s="91"/>
       <c r="E15" s="60"/>
       <c r="F15" s="60"/>
     </row>
@@ -2920,7 +2963,6 @@
       <c r="B16" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="91"/>
       <c r="E16" s="60"/>
       <c r="F16" s="60"/>
     </row>
@@ -2931,7 +2973,6 @@
       <c r="B17" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="91"/>
       <c r="E17" s="60"/>
       <c r="F17" s="60"/>
     </row>
@@ -2942,7 +2983,6 @@
       <c r="B18" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="91"/>
       <c r="E18" s="60"/>
       <c r="F18" s="60"/>
     </row>
@@ -2953,7 +2993,6 @@
       <c r="B19" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="91"/>
       <c r="E19" s="60"/>
       <c r="F19" s="60"/>
     </row>
@@ -2964,7 +3003,6 @@
       <c r="B20" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="91"/>
       <c r="E20" s="60"/>
       <c r="F20" s="60"/>
     </row>
@@ -2975,7 +3013,6 @@
       <c r="B21" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="91"/>
       <c r="E21" s="60"/>
       <c r="F21" s="60"/>
     </row>
@@ -2986,7 +3023,6 @@
       <c r="B22" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="91"/>
       <c r="E22" s="60"/>
       <c r="F22" s="60"/>
     </row>
@@ -2997,7 +3033,6 @@
       <c r="B23" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="91"/>
       <c r="E23" s="60"/>
       <c r="F23" s="60"/>
     </row>
@@ -3008,7 +3043,7 @@
       <c r="B24" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D24" s="90"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="60"/>
       <c r="F24" s="60"/>
     </row>
@@ -3019,7 +3054,6 @@
       <c r="B25" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="91"/>
       <c r="E25" s="60"/>
       <c r="F25" s="60"/>
     </row>
@@ -3030,7 +3064,6 @@
       <c r="B26" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="91"/>
       <c r="E26" s="60"/>
       <c r="F26" s="60"/>
     </row>
@@ -3041,7 +3074,7 @@
       <c r="B27" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D27" s="90"/>
+      <c r="D27" s="89"/>
       <c r="E27" s="60"/>
       <c r="F27" s="60"/>
     </row>
@@ -3052,7 +3085,7 @@
       <c r="B28" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="90"/>
+      <c r="D28" s="89"/>
       <c r="E28" s="60"/>
       <c r="F28" s="60"/>
     </row>
@@ -3063,7 +3096,6 @@
       <c r="B29" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D29" s="91"/>
       <c r="E29" s="60"/>
       <c r="F29" s="60"/>
     </row>
@@ -3074,7 +3106,7 @@
       <c r="B30" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="90"/>
+      <c r="D30" s="89"/>
       <c r="E30" s="60"/>
       <c r="F30" s="60"/>
     </row>
@@ -3085,7 +3117,7 @@
       <c r="B31" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D31" s="90"/>
+      <c r="D31" s="89"/>
       <c r="E31" s="60"/>
       <c r="F31" s="60"/>
     </row>
@@ -3096,7 +3128,7 @@
       <c r="B32" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D32" s="90"/>
+      <c r="D32" s="89"/>
       <c r="E32" s="60"/>
       <c r="F32" s="60"/>
     </row>
@@ -3107,7 +3139,6 @@
       <c r="B33" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="91"/>
       <c r="E33" s="60"/>
       <c r="F33" s="60"/>
     </row>
@@ -3118,7 +3149,6 @@
       <c r="B34" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D34" s="91"/>
       <c r="E34" s="60"/>
       <c r="F34" s="60"/>
     </row>
@@ -3129,7 +3159,6 @@
       <c r="B35" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="91"/>
       <c r="E35" s="60"/>
       <c r="F35" s="60"/>
     </row>
@@ -3140,7 +3169,7 @@
       <c r="B36" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D36" s="90"/>
+      <c r="D36" s="89"/>
       <c r="E36" s="60"/>
       <c r="F36" s="60"/>
     </row>
@@ -3151,7 +3180,6 @@
       <c r="B37" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D37" s="91"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
     </row>
@@ -3162,7 +3190,6 @@
       <c r="B38" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D38" s="91"/>
       <c r="E38" s="60"/>
       <c r="F38" s="60"/>
     </row>
@@ -3173,7 +3200,6 @@
       <c r="B39" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D39" s="91"/>
       <c r="E39" s="60"/>
       <c r="F39" s="60"/>
     </row>
@@ -3184,7 +3210,6 @@
       <c r="B40" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="91"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
     </row>
@@ -3195,18 +3220,16 @@
       <c r="B41" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D41" s="91"/>
       <c r="E41" s="60"/>
       <c r="F41" s="60"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B42" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="D42" s="91"/>
       <c r="E42" s="60"/>
       <c r="F42" s="60"/>
     </row>
@@ -3217,7 +3240,7 @@
       <c r="B43" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="90"/>
+      <c r="D43" s="89"/>
       <c r="E43" s="60"/>
       <c r="F43" s="60"/>
     </row>
@@ -3228,7 +3251,7 @@
       <c r="B44" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D44" s="90"/>
+      <c r="D44" s="89"/>
       <c r="E44" s="60"/>
       <c r="F44" s="60"/>
     </row>
@@ -3239,7 +3262,7 @@
       <c r="B45" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D45" s="90"/>
+      <c r="D45" s="89"/>
       <c r="E45" s="60"/>
       <c r="F45" s="60"/>
     </row>
@@ -3250,7 +3273,7 @@
       <c r="B46" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D46" s="90"/>
+      <c r="D46" s="89"/>
       <c r="E46" s="60"/>
       <c r="F46" s="60"/>
     </row>
@@ -3261,7 +3284,7 @@
       <c r="B47" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D47" s="90"/>
+      <c r="D47" s="89"/>
       <c r="E47" s="60"/>
       <c r="F47" s="60"/>
     </row>
@@ -3272,18 +3295,18 @@
       <c r="B48" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D48" s="90"/>
+      <c r="D48" s="89"/>
       <c r="E48" s="60"/>
       <c r="F48" s="60"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A49" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B49" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D49" s="90"/>
+      <c r="D49" s="89"/>
       <c r="E49" s="60"/>
       <c r="F49" s="60"/>
     </row>
@@ -3294,7 +3317,7 @@
       <c r="B50" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="89"/>
+      <c r="D50" s="26"/>
       <c r="E50" s="60"/>
       <c r="F50" s="60"/>
     </row>
@@ -3305,7 +3328,6 @@
       <c r="B51" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D51" s="91"/>
       <c r="E51" s="60"/>
       <c r="F51" s="60"/>
     </row>
@@ -3316,7 +3338,6 @@
       <c r="B52" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D52" s="91"/>
       <c r="E52" s="60"/>
       <c r="F52" s="60"/>
     </row>
@@ -3328,15 +3349,15 @@
         <v>0</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E53" s="60"/>
       <c r="F53" s="60"/>
       <c r="G53" s="73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
@@ -3347,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E54" s="60"/>
       <c r="F54" s="60"/>
@@ -3363,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="C55" s="22"/>
-      <c r="D55" s="90"/>
+      <c r="D55" s="89"/>
       <c r="E55" s="60"/>
       <c r="F55" s="60"/>
     </row>
@@ -3375,10 +3396,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E56" s="60"/>
       <c r="F56" s="60"/>
@@ -3391,10 +3412,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E57" s="60"/>
       <c r="F57" s="60"/>
@@ -3407,10 +3428,10 @@
         <v>0</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D58" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E58" s="60"/>
       <c r="F58" s="60"/>
@@ -3423,10 +3444,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E59" s="60"/>
       <c r="F59" s="60"/>
@@ -3439,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="22"/>
-      <c r="D60" s="90"/>
+      <c r="D60" s="89"/>
       <c r="E60" s="60"/>
       <c r="F60" s="60"/>
     </row>
@@ -3451,10 +3472,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D61" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E61" s="60"/>
       <c r="F61" s="60"/>
@@ -3464,40 +3485,40 @@
         <v>59</v>
       </c>
       <c r="B62" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="C62" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="C62" s="28" t="s">
-        <v>172</v>
-      </c>
       <c r="D62" s="29" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E62" s="61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F62" s="62" t="s">
         <v>141</v>
       </c>
       <c r="G62" s="57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H62" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I62" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K62" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L62" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M62" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
@@ -3505,21 +3526,21 @@
         <v>60</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D63" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E63" s="60"/>
       <c r="F63" s="60"/>
       <c r="I63" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.45">
@@ -3527,18 +3548,18 @@
         <v>61</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E64" s="60"/>
       <c r="F64" s="60"/>
       <c r="K64" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.45">
@@ -3546,13 +3567,13 @@
         <v>62</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E65" s="60"/>
       <c r="F65" s="60"/>
@@ -3562,13 +3583,13 @@
         <v>63</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C66" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="D66" s="20" t="s">
         <v>391</v>
-      </c>
-      <c r="D66" s="20" t="s">
-        <v>392</v>
       </c>
       <c r="E66" s="60"/>
       <c r="F66" s="60"/>
@@ -3578,29 +3599,29 @@
         <v>64</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E67" s="60"/>
       <c r="F67" s="60"/>
     </row>
     <row r="68" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B68" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B68" s="17" t="s">
-        <v>176</v>
-      </c>
       <c r="C68" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D68" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E68" s="63"/>
       <c r="F68" s="63"/>
@@ -3610,16 +3631,16 @@
     </row>
     <row r="69" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C69" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E69" s="63"/>
       <c r="F69" s="63"/>
@@ -3629,16 +3650,16 @@
     </row>
     <row r="70" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A70" s="32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E70" s="63"/>
       <c r="F70" s="63"/>
@@ -3648,16 +3669,16 @@
     </row>
     <row r="71" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A71" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C71" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="D71" s="29" t="s">
         <v>179</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="C71" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="D71" s="29" t="s">
-        <v>180</v>
       </c>
       <c r="E71" s="63"/>
       <c r="F71" s="63"/>
@@ -3670,35 +3691,35 @@
         <v>65</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C72" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="D72" s="29" t="s">
         <v>393</v>
-      </c>
-      <c r="D72" s="29" t="s">
-        <v>394</v>
       </c>
       <c r="E72" s="60"/>
       <c r="F72" s="64" t="s">
         <v>142</v>
       </c>
       <c r="G72" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="H72" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="I72" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="H72" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="I72" s="21" t="s">
-        <v>182</v>
-      </c>
       <c r="K72" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L72" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M72" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.45">
@@ -3706,16 +3727,16 @@
         <v>66</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C73" s="22"/>
       <c r="D73" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E73" s="60"/>
       <c r="F73" s="65"/>
       <c r="K73" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
@@ -3723,15 +3744,17 @@
         <v>67</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D74" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="E74" s="60"/>
+        <v>391</v>
+      </c>
+      <c r="E74" s="60" t="s">
+        <v>404</v>
+      </c>
       <c r="F74" s="62" t="s">
         <v>143</v>
       </c>
@@ -3741,13 +3764,13 @@
         <v>68</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E75" s="60"/>
       <c r="F75" s="60"/>
@@ -3757,32 +3780,34 @@
         <v>69</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="E76" s="60"/>
+        <v>179</v>
+      </c>
+      <c r="E76" s="60" t="s">
+        <v>403</v>
+      </c>
       <c r="F76" s="60"/>
       <c r="M76" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="77" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A77" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B77" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="D77" s="29" t="s">
         <v>183</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="C77" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>184</v>
       </c>
       <c r="E77" s="63"/>
       <c r="F77" s="63"/>
@@ -3795,21 +3820,21 @@
         <v>70</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E78" s="60"/>
       <c r="F78" s="60"/>
       <c r="G78" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M78" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="57" x14ac:dyDescent="0.45">
@@ -3817,27 +3842,27 @@
         <v>71</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E79" s="60"/>
       <c r="F79" s="60"/>
       <c r="G79" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I79" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K79" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L79" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="57" x14ac:dyDescent="0.45">
@@ -3845,33 +3870,33 @@
         <v>72</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C80" s="28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E80" s="60"/>
       <c r="F80" s="60"/>
       <c r="G80" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="H80" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="H80" s="21" t="s">
-        <v>189</v>
-      </c>
       <c r="I80" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K80" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L80" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M80" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="57" x14ac:dyDescent="0.45">
@@ -3879,24 +3904,24 @@
         <v>73</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C81" s="28" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E81" s="60"/>
       <c r="F81" s="60"/>
       <c r="G81" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H81" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I81" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.45">
@@ -3904,29 +3929,29 @@
         <v>74</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D82" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E82" s="60"/>
       <c r="F82" s="60"/>
     </row>
     <row r="83" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E83" s="63"/>
       <c r="F83" s="63"/>
@@ -3936,16 +3961,16 @@
     </row>
     <row r="84" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C84" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E84" s="63"/>
       <c r="F84" s="63"/>
@@ -3955,16 +3980,16 @@
     </row>
     <row r="85" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E85" s="63"/>
       <c r="F85" s="63"/>
@@ -3974,16 +3999,16 @@
     </row>
     <row r="86" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E86" s="63"/>
       <c r="F86" s="63"/>
@@ -3996,13 +4021,13 @@
         <v>75</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C87" s="28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E87" s="60"/>
       <c r="F87" s="60"/>
@@ -4012,13 +4037,13 @@
         <v>76</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E88" s="60"/>
       <c r="F88" s="60"/>
@@ -4028,13 +4053,13 @@
         <v>77</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E89" s="60"/>
       <c r="F89" s="60"/>
@@ -4044,13 +4069,13 @@
         <v>78</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D90" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E90" s="60"/>
       <c r="F90" s="60"/>
@@ -4060,23 +4085,23 @@
         <v>79</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C91" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="D91" s="20" t="s">
         <v>396</v>
-      </c>
-      <c r="D91" s="20" t="s">
-        <v>397</v>
       </c>
       <c r="E91" s="60"/>
       <c r="F91" s="62" t="s">
         <v>144</v>
       </c>
       <c r="K91" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L91" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.45">
@@ -4084,29 +4109,29 @@
         <v>80</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D92" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E92" s="60"/>
       <c r="F92" s="60"/>
     </row>
     <row r="93" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D93" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E93" s="63"/>
       <c r="F93" s="63"/>
@@ -4119,13 +4144,13 @@
         <v>81</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D94" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E94" s="60"/>
       <c r="F94" s="60"/>
@@ -4135,13 +4160,13 @@
         <v>82</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C95" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D95" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E95" s="60"/>
       <c r="F95" s="60"/>
@@ -4151,29 +4176,29 @@
         <v>83</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C96" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D96" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E96" s="60"/>
       <c r="F96" s="60"/>
     </row>
     <row r="97" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D97" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E97" s="63"/>
       <c r="F97" s="63"/>
@@ -4183,16 +4208,16 @@
     </row>
     <row r="98" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A98" s="32" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D98" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E98" s="63"/>
       <c r="F98" s="63"/>
@@ -4202,16 +4227,16 @@
     </row>
     <row r="99" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="B99" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C99" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="D99" s="34" t="s">
         <v>200</v>
-      </c>
-      <c r="B99" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="C99" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="D99" s="34" t="s">
-        <v>201</v>
       </c>
       <c r="E99" s="63"/>
       <c r="F99" s="63"/>
@@ -4221,16 +4246,16 @@
     </row>
     <row r="100" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D100" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E100" s="63"/>
       <c r="F100" s="63"/>
@@ -4243,29 +4268,29 @@
         <v>84</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D101" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E101" s="60"/>
       <c r="F101" s="60"/>
     </row>
     <row r="102" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C102" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D102" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E102" s="63"/>
       <c r="F102" s="63"/>
@@ -4275,16 +4300,16 @@
     </row>
     <row r="103" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C103" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E103" s="63"/>
       <c r="F103" s="63"/>
@@ -4297,18 +4322,18 @@
         <v>85</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D104" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E104" s="60"/>
       <c r="F104" s="60"/>
       <c r="K104" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.45">
@@ -4316,26 +4341,26 @@
         <v>86</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D105" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="E105" s="66" t="s">
-        <v>145</v>
+        <v>391</v>
+      </c>
+      <c r="E105" s="90" t="s">
+        <v>402</v>
       </c>
       <c r="F105" s="60"/>
       <c r="K105" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L105" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M105" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.45">
@@ -4343,21 +4368,21 @@
         <v>87</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C106" s="35" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D106" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E106" s="66"/>
       <c r="F106" s="60"/>
       <c r="K106" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M106" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="71.25" x14ac:dyDescent="0.45">
@@ -4365,26 +4390,26 @@
         <v>88</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D107" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="E107" s="66" t="s">
-        <v>145</v>
+        <v>391</v>
+      </c>
+      <c r="E107" s="90" t="s">
+        <v>402</v>
       </c>
       <c r="F107" s="60"/>
       <c r="G107" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H107" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I107" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.45">
@@ -4392,13 +4417,13 @@
         <v>89</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D108" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E108" s="66"/>
       <c r="F108" s="60"/>
@@ -4408,20 +4433,20 @@
         <v>90</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D109" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="E109" s="66" t="s">
-        <v>145</v>
+        <v>391</v>
+      </c>
+      <c r="E109" s="90" t="s">
+        <v>402</v>
       </c>
       <c r="F109" s="60"/>
       <c r="I109" s="21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.45">
@@ -4429,26 +4454,26 @@
         <v>91</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C110" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D110" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E110" s="60"/>
       <c r="F110" s="60"/>
     </row>
     <row r="111" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C111" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D111" s="26"/>
       <c r="E111" s="63"/>
@@ -4459,13 +4484,13 @@
     </row>
     <row r="112" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C112" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D112" s="26"/>
       <c r="E112" s="63"/>
@@ -4476,16 +4501,16 @@
     </row>
     <row r="113" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C113" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D113" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E113" s="63"/>
       <c r="F113" s="63"/>
@@ -4498,7 +4523,7 @@
         <v>92</v>
       </c>
       <c r="B114" s="36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D114" s="37"/>
       <c r="E114" s="63"/>
@@ -4509,10 +4534,10 @@
     </row>
     <row r="115" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B115" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D115" s="37"/>
       <c r="E115" s="63"/>
@@ -4523,10 +4548,10 @@
     </row>
     <row r="116" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B116" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D116" s="38"/>
       <c r="E116" s="63"/>
@@ -4540,13 +4565,13 @@
         <v>93</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D117" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E117" s="60"/>
       <c r="F117" s="60"/>
@@ -4556,13 +4581,13 @@
         <v>94</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C118" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D118" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E118" s="60"/>
       <c r="F118" s="60"/>
@@ -4572,18 +4597,20 @@
         <v>95</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="E119" s="60"/>
+        <v>184</v>
+      </c>
+      <c r="E119" s="60" t="s">
+        <v>403</v>
+      </c>
       <c r="F119" s="60"/>
       <c r="M119" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.45">
@@ -4591,26 +4618,26 @@
         <v>96</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C120" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D120" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E120" s="60"/>
       <c r="F120" s="60"/>
     </row>
     <row r="121" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C121" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D121" s="26"/>
       <c r="E121" s="63"/>
@@ -4621,16 +4648,16 @@
     </row>
     <row r="122" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C122" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D122" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E122" s="63"/>
       <c r="F122" s="63"/>
@@ -4643,7 +4670,7 @@
         <v>97</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="63"/>
@@ -4657,19 +4684,19 @@
         <v>98</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="63"/>
       <c r="F124" s="63"/>
       <c r="G124" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="42.75" x14ac:dyDescent="0.45">
@@ -4677,35 +4704,35 @@
         <v>99</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C125" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D125" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="E125" s="66" t="s">
-        <v>145</v>
+        <v>184</v>
+      </c>
+      <c r="E125" s="90" t="s">
+        <v>402</v>
       </c>
       <c r="F125" s="65"/>
       <c r="G125" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H125" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I125" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K125" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L125" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M125" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.45">
@@ -4713,16 +4740,16 @@
         <v>100</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D126" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="E126" s="66" t="s">
-        <v>145</v>
+        <v>200</v>
+      </c>
+      <c r="E126" s="90" t="s">
+        <v>402</v>
       </c>
       <c r="F126" s="62" t="s">
         <v>142</v>
@@ -4730,15 +4757,15 @@
     </row>
     <row r="127" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C127" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="D127" s="89"/>
+        <v>168</v>
+      </c>
+      <c r="D127" s="26"/>
       <c r="E127" s="63"/>
       <c r="F127" s="63"/>
       <c r="G127" s="6"/>
@@ -4747,15 +4774,15 @@
     </row>
     <row r="128" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C128" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="D128" s="89"/>
+        <v>168</v>
+      </c>
+      <c r="D128" s="26"/>
       <c r="E128" s="63"/>
       <c r="F128" s="63"/>
       <c r="G128" s="6"/>
@@ -4764,15 +4791,15 @@
     </row>
     <row r="129" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C129" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="D129" s="89"/>
+        <v>168</v>
+      </c>
+      <c r="D129" s="26"/>
       <c r="E129" s="63"/>
       <c r="F129" s="63"/>
       <c r="G129" s="6"/>
@@ -4781,15 +4808,15 @@
     </row>
     <row r="130" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C130" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="D130" s="89"/>
+        <v>168</v>
+      </c>
+      <c r="D130" s="26"/>
       <c r="E130" s="63"/>
       <c r="F130" s="63"/>
       <c r="G130" s="6"/>
@@ -4801,13 +4828,13 @@
         <v>101</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D131" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E131" s="60"/>
       <c r="F131" s="60"/>
@@ -4817,18 +4844,18 @@
         <v>102</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D132" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E132" s="60"/>
       <c r="F132" s="60"/>
       <c r="K132" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.45">
@@ -4836,13 +4863,13 @@
         <v>103</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D133" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E133" s="60"/>
       <c r="F133" s="60"/>
@@ -4852,26 +4879,26 @@
         <v>104</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D134" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E134" s="60"/>
       <c r="F134" s="60"/>
     </row>
     <row r="135" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A135" s="30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C135" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D135" s="37"/>
       <c r="E135" s="63"/>
@@ -4885,7 +4912,7 @@
         <v>105</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D136" s="37"/>
       <c r="E136" s="63"/>
@@ -4899,17 +4926,17 @@
         <v>106</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C137" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D137" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E137" s="60"/>
       <c r="F137" s="60" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.45">
@@ -4917,17 +4944,17 @@
         <v>107</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D138" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E138" s="60"/>
       <c r="F138" s="60" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.45">
@@ -4935,17 +4962,17 @@
         <v>108</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C139" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D139" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E139" s="60"/>
       <c r="F139" s="62" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.45">
@@ -4953,24 +4980,24 @@
         <v>109</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>392</v>
-      </c>
-      <c r="D140" s="90"/>
+        <v>391</v>
+      </c>
+      <c r="D140" s="89"/>
       <c r="E140" s="60"/>
       <c r="F140" s="60"/>
     </row>
     <row r="141" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A141" s="30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C141" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D141" s="37"/>
       <c r="E141" s="63"/>
@@ -4981,13 +5008,13 @@
     </row>
     <row r="142" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A142" s="30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C142" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D142" s="37"/>
       <c r="E142" s="63"/>
@@ -5001,7 +5028,7 @@
         <v>110</v>
       </c>
       <c r="B143" s="36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D143" s="37"/>
       <c r="E143" s="63"/>
@@ -5015,7 +5042,7 @@
         <v>111</v>
       </c>
       <c r="B144" s="36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D144" s="37"/>
       <c r="E144" s="63"/>
@@ -5026,10 +5053,10 @@
     </row>
     <row r="145" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A145" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B145" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D145" s="37"/>
       <c r="E145" s="63"/>
@@ -5043,30 +5070,30 @@
         <v>112</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D146" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E146" s="60"/>
       <c r="F146" s="60"/>
       <c r="G146" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H146" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I146" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K146" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L146" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M146" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.45">
@@ -5074,9 +5101,9 @@
         <v>113</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="D147" s="90"/>
+        <v>173</v>
+      </c>
+      <c r="D147" s="89"/>
       <c r="E147" s="60"/>
       <c r="F147" s="60"/>
     </row>
@@ -5102,10 +5129,10 @@
         <v>0</v>
       </c>
       <c r="C149" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D149" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E149" s="60"/>
       <c r="F149" s="60"/>
@@ -5118,10 +5145,10 @@
         <v>0</v>
       </c>
       <c r="C150" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D150" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E150" s="60"/>
       <c r="F150" s="60"/>
@@ -5134,10 +5161,10 @@
         <v>0</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D151" s="20" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E151" s="60"/>
       <c r="F151" s="60"/>
@@ -5150,10 +5177,10 @@
         <v>0</v>
       </c>
       <c r="C152" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D152" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E152" s="60"/>
       <c r="F152" s="60"/>
@@ -5292,10 +5319,10 @@
         <v>134</v>
       </c>
       <c r="C166" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D166" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E166" s="60"/>
       <c r="F166" s="60"/>
@@ -5308,10 +5335,10 @@
         <v>134</v>
       </c>
       <c r="C167" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D167" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E167" s="60"/>
       <c r="F167" s="60"/>
@@ -5324,17 +5351,17 @@
         <v>134</v>
       </c>
       <c r="C168" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D168" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E168" s="60"/>
       <c r="F168" s="60"/>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B169" s="17">
         <f>COUNTIF($B$2:$B$168,"A")</f>
@@ -5350,7 +5377,7 @@
       </c>
       <c r="E169" s="67">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F169" s="67">
         <f t="shared" si="0"/>
@@ -5387,7 +5414,7 @@
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B170" s="17">
         <f>COUNTIF($B$2:$B$168,"AA")</f>
@@ -5403,7 +5430,7 @@
       </c>
       <c r="E170" s="68">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F170" s="68">
         <f t="shared" si="2"/>
@@ -5440,7 +5467,7 @@
     </row>
     <row r="171" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A171" s="39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B171" s="37">
         <f>COUNTIF($B$2:$B$168,"AAA")</f>
@@ -5482,7 +5509,7 @@
     </row>
     <row r="172" spans="1:13" s="33" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B172" s="42">
         <f>COUNTIF($B$2:$B$168,"shall")</f>
@@ -5535,7 +5562,7 @@
     </row>
     <row r="173" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A173" s="48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B173" s="46">
         <f>COUNTIF($B$2:$B$168,"should")</f>
@@ -5590,7 +5617,7 @@
       </c>
       <c r="E174" s="71">
         <f>SUM(E169:E173)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F174" s="71">
         <f>SUM(F169:F173)</f>
@@ -5640,7 +5667,7 @@
       </c>
       <c r="E175" s="71">
         <f>E$169+E$170+E172</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F175" s="71">
         <f>F$169+F$170+F172</f>
@@ -5677,86 +5704,101 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A67">
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="7" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A76 A78:A82 A87:A92 A94:A96 A101">
+    <cfRule type="cellIs" dxfId="21" priority="23" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A104:A111">
+    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A114">
+    <cfRule type="cellIs" dxfId="19" priority="21" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A117:A120">
+    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A123:A126 A131:A134">
     <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A104:A111">
+  <conditionalFormatting sqref="A136:A140">
     <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A114">
+  <conditionalFormatting sqref="A143:A144">
     <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A117:A120">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A123:A126 A131:A134">
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A136:A140">
-    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A143:A144">
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A166:A168">
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C149:C152 C169:M173">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"manuell"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:F1 C3 D30:F32 C117:C122 C125:C135 C137:C142 C166:C168 C193:C1048576 C53:F113">
-    <cfRule type="cellIs" dxfId="8" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="26" operator="equal">
+      <formula>"manuell"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D140">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+      <formula>"manuell"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D147">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"manuell"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F2">
-    <cfRule type="cellIs" dxfId="7" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="27" operator="equal">
       <formula>"nicht abgedeckt"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:F4 D24:F24 D27:F28 D36:F36 D43:F50 D117:F131">
-    <cfRule type="cellIs" dxfId="6" priority="27" operator="equal">
+  <conditionalFormatting sqref="D2:F4 D24:F24 D27:F28 D36:F36 D43:F50 D117:F118 D127:F131 D125:D126 F125:F126 D120:F124 D119 F119">
+    <cfRule type="cellIs" dxfId="8" priority="31" operator="equal">
       <formula>"manuell"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F132">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
       <formula>"manuell"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F137:F138">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"manuell"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D140">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <conditionalFormatting sqref="E125">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"manuell"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D147">
+  <conditionalFormatting sqref="E126">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"manuell"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E119">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"manuell"</formula>
     </cfRule>
@@ -5781,19 +5823,19 @@
   <sheetData>
     <row r="1" spans="1:138" s="9" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="79" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C1" s="79" t="s">
+      <c r="D1" s="79" t="s">
         <v>245</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="E1" s="79" t="s">
         <v>246</v>
-      </c>
-      <c r="E1" s="79" t="s">
-        <v>247</v>
       </c>
       <c r="F1" s="13"/>
       <c r="G1" s="53"/>
@@ -5931,7 +5973,7 @@
     </row>
     <row r="2" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A2" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B2" s="82" t="s">
         <v>0</v>
@@ -5940,7 +5982,7 @@
     </row>
     <row r="3" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A3" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" s="82" t="s">
         <v>0</v>
@@ -5948,7 +5990,7 @@
     </row>
     <row r="4" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A4" s="33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" s="82" t="s">
         <v>0</v>
@@ -5956,7 +5998,7 @@
     </row>
     <row r="5" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A5" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B5" s="82" t="s">
         <v>0</v>
@@ -5964,7 +6006,7 @@
     </row>
     <row r="6" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A6" s="33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B6" s="82" t="s">
         <v>0</v>
@@ -5972,7 +6014,7 @@
     </row>
     <row r="7" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A7" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B7" s="82" t="s">
         <v>0</v>
@@ -5980,7 +6022,7 @@
     </row>
     <row r="8" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B8" s="82" t="s">
         <v>0</v>
@@ -5988,7 +6030,7 @@
     </row>
     <row r="9" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A9" s="33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B9" s="82" t="s">
         <v>0</v>
@@ -5996,7 +6038,7 @@
     </row>
     <row r="10" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A10" s="33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B10" s="82" t="s">
         <v>0</v>
@@ -6004,7 +6046,7 @@
     </row>
     <row r="11" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A11" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B11" s="82" t="s">
         <v>0</v>
@@ -6012,7 +6054,7 @@
     </row>
     <row r="12" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A12" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B12" s="82" t="s">
         <v>0</v>
@@ -6020,7 +6062,7 @@
     </row>
     <row r="13" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A13" s="33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B13" s="82" t="s">
         <v>0</v>
@@ -6028,7 +6070,7 @@
     </row>
     <row r="14" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A14" s="33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B14" s="82" t="s">
         <v>0</v>
@@ -6036,7 +6078,7 @@
     </row>
     <row r="15" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A15" s="80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B15" s="82" t="s">
         <v>0</v>
@@ -6044,7 +6086,7 @@
     </row>
     <row r="16" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A16" s="19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B16" s="82" t="s">
         <v>0</v>
@@ -6052,7 +6094,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B17" s="82" t="s">
         <v>0</v>
@@ -6060,7 +6102,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" s="19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B18" s="82" t="s">
         <v>0</v>
@@ -6068,7 +6110,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B19" s="82" t="s">
         <v>0</v>
@@ -6076,7 +6118,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B20" s="82" t="s">
         <v>0</v>
@@ -6084,7 +6126,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B21" s="82" t="s">
         <v>0</v>
@@ -6092,7 +6134,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B22" s="82" t="s">
         <v>0</v>
@@ -6100,7 +6142,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B23" s="82" t="s">
         <v>0</v>
@@ -6412,7 +6454,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A62" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B62" s="82" t="s">
         <v>0</v>
@@ -6468,7 +6510,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A69" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B69" s="82" t="s">
         <v>0</v>
@@ -6564,26 +6606,26 @@
     </row>
     <row r="81" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A81" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B81" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A82" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B82" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A83" s="19" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B83" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F83"/>
       <c r="G83"/>
@@ -6725,10 +6767,10 @@
     </row>
     <row r="84" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A84" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B84" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F84"/>
       <c r="G84"/>
@@ -6870,10 +6912,10 @@
     </row>
     <row r="85" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A85" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B85" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F85"/>
       <c r="G85"/>
@@ -7015,10 +7057,10 @@
     </row>
     <row r="86" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A86" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B86" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F86"/>
       <c r="G86"/>
@@ -7160,10 +7202,10 @@
     </row>
     <row r="87" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A87" s="19" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B87" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F87"/>
       <c r="G87"/>
@@ -7305,10 +7347,10 @@
     </row>
     <row r="88" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A88" s="19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B88" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F88"/>
       <c r="G88"/>
@@ -7450,10 +7492,10 @@
     </row>
     <row r="89" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A89" s="19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B89" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F89"/>
       <c r="G89"/>
@@ -7595,10 +7637,10 @@
     </row>
     <row r="90" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A90" s="19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B90" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F90"/>
       <c r="G90"/>
@@ -7740,10 +7782,10 @@
     </row>
     <row r="91" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A91" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B91" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F91"/>
       <c r="G91"/>
@@ -7885,10 +7927,10 @@
     </row>
     <row r="92" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A92" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B92" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F92"/>
       <c r="G92"/>
@@ -8030,10 +8072,10 @@
     </row>
     <row r="93" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A93" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F93"/>
       <c r="G93"/>
@@ -8175,10 +8217,10 @@
     </row>
     <row r="94" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A94" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B94" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F94"/>
       <c r="G94"/>
@@ -8320,10 +8362,10 @@
     </row>
     <row r="95" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A95" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B95" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F95"/>
       <c r="G95"/>
@@ -8465,10 +8507,10 @@
     </row>
     <row r="96" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A96" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B96" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F96"/>
       <c r="G96"/>
@@ -8610,10 +8652,10 @@
     </row>
     <row r="97" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A97" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B97" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F97"/>
       <c r="G97"/>
@@ -8755,10 +8797,10 @@
     </row>
     <row r="98" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A98" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B98" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F98"/>
       <c r="G98"/>
@@ -8900,10 +8942,10 @@
     </row>
     <row r="99" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A99" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B99" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F99"/>
       <c r="G99"/>
@@ -9045,10 +9087,10 @@
     </row>
     <row r="100" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A100" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B100" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F100"/>
       <c r="G100"/>
@@ -9190,10 +9232,10 @@
     </row>
     <row r="101" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A101" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B101" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F101"/>
       <c r="G101"/>
@@ -9335,10 +9377,10 @@
     </row>
     <row r="102" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A102" s="19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B102" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F102"/>
       <c r="G102"/>
@@ -9480,10 +9522,10 @@
     </row>
     <row r="103" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A103" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B103" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F103"/>
       <c r="G103"/>
@@ -9625,10 +9667,10 @@
     </row>
     <row r="104" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A104" s="19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B104" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F104"/>
       <c r="G104"/>
@@ -9770,10 +9812,10 @@
     </row>
     <row r="105" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A105" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B105" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F105"/>
       <c r="G105"/>
@@ -9915,10 +9957,10 @@
     </row>
     <row r="106" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A106" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B106" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F106"/>
       <c r="G106"/>
@@ -10060,10 +10102,10 @@
     </row>
     <row r="107" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A107" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B107" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F107"/>
       <c r="G107"/>
@@ -10205,10 +10247,10 @@
     </row>
     <row r="108" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A108" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B108" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F108"/>
       <c r="G108"/>
@@ -10350,10 +10392,10 @@
     </row>
     <row r="109" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A109" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B109" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F109"/>
       <c r="G109"/>
@@ -10495,10 +10537,10 @@
     </row>
     <row r="110" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A110" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B110" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F110"/>
       <c r="G110"/>
@@ -10640,10 +10682,10 @@
     </row>
     <row r="111" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A111" s="27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B111" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F111"/>
       <c r="G111"/>
@@ -10785,10 +10827,10 @@
     </row>
     <row r="112" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A112" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B112" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F112"/>
       <c r="G112"/>
@@ -10930,10 +10972,10 @@
     </row>
     <row r="113" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A113" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B113" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F113"/>
       <c r="G113"/>
@@ -11075,10 +11117,10 @@
     </row>
     <row r="114" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A114" s="19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B114" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F114"/>
       <c r="G114"/>
@@ -11220,115 +11262,115 @@
     </row>
     <row r="115" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A115" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B115" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="116" spans="1:142" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="81" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B116" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="117" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A117" s="81" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B117" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="118" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A118" s="19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B118" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="119" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A119" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B119" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C119" s="73"/>
     </row>
     <row r="120" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A120" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B120" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="121" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A121" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B121" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="122" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A122" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B122" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="123" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A123" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B123" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="124" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A124" s="27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B124" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="125" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A125" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B125" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A126" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B126" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="127" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A127" s="19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B127" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="128" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A128" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B128" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C128" s="57"/>
       <c r="D128" s="21"/>
@@ -11337,41 +11379,41 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A129" s="27" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B129" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E129" s="21"/>
       <c r="F129" s="6"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A130" s="27" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B130" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A131" s="19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B131" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A132" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B132" s="88" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A133" s="27" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B133" s="87" t="s">
         <v>0</v>
@@ -11379,10 +11421,10 @@
     </row>
     <row r="134" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A134" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B134" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="6"/>
@@ -11390,10 +11432,10 @@
     </row>
     <row r="135" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A135" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B135" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C135" s="6"/>
       <c r="D135" s="6"/>
@@ -11401,10 +11443,10 @@
     </row>
     <row r="136" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A136" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B136" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="6"/>
@@ -11412,10 +11454,10 @@
     </row>
     <row r="137" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A137" s="19" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B137" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C137" s="6"/>
       <c r="D137" s="6"/>
@@ -11423,10 +11465,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A138" s="19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B138" s="82" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C138" s="21"/>
       <c r="D138" s="21"/>
@@ -11434,42 +11476,42 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A139" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B139" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A140" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B140" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A141" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B141" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A142" s="19" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="143" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A143" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
@@ -11477,29 +11519,29 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A144" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C144" s="21"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C145" s="21"/>
       <c r="E145" s="21"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C146" s="21"/>
       <c r="D146" s="21"/>
@@ -11507,10 +11549,10 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C147" s="21"/>
       <c r="D147" s="21"/>
@@ -11518,18 +11560,18 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A149" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C149" s="6"/>
       <c r="D149" s="6"/>
@@ -11537,10 +11579,10 @@
     </row>
     <row r="150" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A150" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="6"/>
@@ -11548,10 +11590,10 @@
     </row>
     <row r="151" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A151" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C151" s="6"/>
       <c r="D151" s="6"/>
@@ -11559,10 +11601,10 @@
     </row>
     <row r="152" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A152" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
@@ -11570,58 +11612,58 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A159" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C159" s="6"/>
       <c r="D159" s="6"/>
@@ -11629,34 +11671,34 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="163" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A163" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C163" s="6"/>
       <c r="D163" s="6"/>
@@ -11664,10 +11706,10 @@
     </row>
     <row r="164" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A164" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B164" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="6"/>
@@ -11675,10 +11717,10 @@
     </row>
     <row r="165" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A165" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C165" s="6"/>
       <c r="D165" s="6"/>
@@ -11686,10 +11728,10 @@
     </row>
     <row r="166" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A166" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="6"/>
@@ -11697,18 +11739,18 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" s="19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A168" s="19" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="6"/>
@@ -11716,10 +11758,10 @@
     </row>
     <row r="169" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A169" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C169" s="6"/>
       <c r="D169" s="6"/>
@@ -11727,34 +11769,34 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" s="19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C173" s="21"/>
       <c r="D173" s="21"/>
@@ -11762,35 +11804,35 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B175" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E175" s="21"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" s="19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="177" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A177" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C177" s="6"/>
       <c r="D177" s="6"/>
@@ -11798,10 +11840,10 @@
     </row>
     <row r="178" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A178" s="19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="6"/>
@@ -11809,10 +11851,10 @@
     </row>
     <row r="179" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A179" s="27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B179" s="42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C179" s="6"/>
       <c r="D179" s="6"/>
@@ -11820,10 +11862,10 @@
     </row>
     <row r="180" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A180" s="27" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B180" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="6"/>
@@ -11831,10 +11873,10 @@
     </row>
     <row r="181" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A181" s="19" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C181" s="6"/>
       <c r="D181" s="6"/>
@@ -11842,10 +11884,10 @@
     </row>
     <row r="182" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A182" s="19" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B182" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="6"/>
@@ -11853,7 +11895,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B183" s="17" t="s">
         <v>0</v>
@@ -11861,7 +11903,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B184" s="17" t="s">
         <v>0</v>
@@ -11869,7 +11911,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B185" s="17" t="s">
         <v>0</v>
@@ -11877,7 +11919,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" s="19" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B186" s="17" t="s">
         <v>0</v>
@@ -11885,7 +11927,7 @@
     </row>
     <row r="187" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A187" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B187" s="17" t="s">
         <v>0</v>
@@ -11896,7 +11938,7 @@
     </row>
     <row r="188" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A188" s="19" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B188" s="17" t="s">
         <v>0</v>
@@ -11907,7 +11949,7 @@
     </row>
     <row r="189" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A189" s="19" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B189" s="17" t="s">
         <v>0</v>
@@ -11918,7 +11960,7 @@
     </row>
     <row r="190" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A190" s="19" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B190" s="17" t="s">
         <v>0</v>
@@ -11929,7 +11971,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B191" s="17" t="s">
         <v>0</v>
@@ -11940,7 +11982,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192" s="19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B192" s="17" t="s">
         <v>0</v>
@@ -11948,7 +11990,7 @@
     </row>
     <row r="193" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A193" s="19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B193" s="17" t="s">
         <v>0</v>
@@ -11959,7 +12001,7 @@
     </row>
     <row r="194" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A194" s="19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B194" s="17" t="s">
         <v>0</v>
@@ -11970,7 +12012,7 @@
     </row>
     <row r="195" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A195" s="19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B195" s="17" t="s">
         <v>0</v>
@@ -11981,7 +12023,7 @@
     </row>
     <row r="196" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A196" s="19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B196" s="17" t="s">
         <v>0</v>
@@ -11992,7 +12034,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="19" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B197" s="17" t="s">
         <v>0</v>
@@ -12000,7 +12042,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" s="19" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B198" s="17" t="s">
         <v>0</v>
@@ -12008,7 +12050,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="19" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B199" s="17" t="s">
         <v>0</v>
@@ -12016,7 +12058,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" s="19" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B200" s="17" t="s">
         <v>0</v>
@@ -12185,7 +12227,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B218" s="17">
         <f>COUNTIF($B$2:$B$217,"A")</f>
@@ -12222,7 +12264,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B219" s="17">
         <f>COUNTIF($B$2:$B$217,"AA")</f>
@@ -12259,7 +12301,7 @@
     </row>
     <row r="220" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A220" s="39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B220" s="37">
         <f>COUNTIF($B$2:$B$217,"AAA")</f>
@@ -12296,7 +12338,7 @@
     </row>
     <row r="221" spans="1:9" s="33" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B221" s="42">
         <f>COUNTIF($B$2:$B$217,"shall")</f>
@@ -12333,7 +12375,7 @@
     </row>
     <row r="222" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A222" s="48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B222" s="46">
         <f>COUNTIF($B$2:$B$217,"should")</f>
@@ -12438,7 +12480,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B214">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12462,19 +12504,19 @@
   <sheetData>
     <row r="1" spans="1:138" s="9" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="79" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C1" s="79" t="s">
+      <c r="D1" s="79" t="s">
         <v>245</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="E1" s="79" t="s">
         <v>246</v>
-      </c>
-      <c r="E1" s="79" t="s">
-        <v>247</v>
       </c>
       <c r="F1" s="13"/>
       <c r="G1" s="53"/>
@@ -12612,7 +12654,7 @@
     </row>
     <row r="2" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A2" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B2" s="82" t="s">
         <v>0</v>
@@ -12621,7 +12663,7 @@
     </row>
     <row r="3" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A3" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" s="82" t="s">
         <v>0</v>
@@ -12629,7 +12671,7 @@
     </row>
     <row r="4" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A4" s="33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" s="82" t="s">
         <v>0</v>
@@ -12637,7 +12679,7 @@
     </row>
     <row r="5" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A5" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B5" s="82" t="s">
         <v>0</v>
@@ -12645,7 +12687,7 @@
     </row>
     <row r="6" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A6" s="33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B6" s="82" t="s">
         <v>0</v>
@@ -12653,7 +12695,7 @@
     </row>
     <row r="7" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A7" s="33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B7" s="82" t="s">
         <v>0</v>
@@ -12661,7 +12703,7 @@
     </row>
     <row r="8" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B8" s="82" t="s">
         <v>0</v>
@@ -12669,7 +12711,7 @@
     </row>
     <row r="9" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A9" s="33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B9" s="82" t="s">
         <v>0</v>
@@ -12677,7 +12719,7 @@
     </row>
     <row r="10" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A10" s="33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B10" s="82" t="s">
         <v>0</v>
@@ -12685,7 +12727,7 @@
     </row>
     <row r="11" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A11" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B11" s="82" t="s">
         <v>0</v>
@@ -12693,7 +12735,7 @@
     </row>
     <row r="12" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A12" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B12" s="82" t="s">
         <v>0</v>
@@ -12701,7 +12743,7 @@
     </row>
     <row r="13" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A13" s="33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B13" s="82" t="s">
         <v>0</v>
@@ -12709,7 +12751,7 @@
     </row>
     <row r="14" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A14" s="33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B14" s="82" t="s">
         <v>0</v>
@@ -12717,7 +12759,7 @@
     </row>
     <row r="15" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A15" s="80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B15" s="82" t="s">
         <v>0</v>
@@ -12725,7 +12767,7 @@
     </row>
     <row r="16" spans="1:138" x14ac:dyDescent="0.45">
       <c r="A16" s="19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B16" s="82" t="s">
         <v>0</v>
@@ -12733,7 +12775,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B17" s="82" t="s">
         <v>0</v>
@@ -12741,7 +12783,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" s="19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B18" s="82" t="s">
         <v>0</v>
@@ -12749,7 +12791,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B19" s="82" t="s">
         <v>0</v>
@@ -12757,7 +12799,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B20" s="82" t="s">
         <v>0</v>
@@ -12765,7 +12807,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B21" s="82" t="s">
         <v>0</v>
@@ -12773,7 +12815,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B22" s="82" t="s">
         <v>0</v>
@@ -12781,7 +12823,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B23" s="82" t="s">
         <v>0</v>
@@ -13093,7 +13135,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A62" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B62" s="82" t="s">
         <v>0</v>
@@ -13149,7 +13191,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A69" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B69" s="82" t="s">
         <v>0</v>
@@ -13245,26 +13287,26 @@
     </row>
     <row r="81" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A81" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B81" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A82" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B82" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A83" s="19" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B83" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F83"/>
       <c r="G83"/>
@@ -13406,10 +13448,10 @@
     </row>
     <row r="84" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A84" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B84" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F84"/>
       <c r="G84"/>
@@ -13551,10 +13593,10 @@
     </row>
     <row r="85" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A85" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B85" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F85"/>
       <c r="G85"/>
@@ -13696,10 +13738,10 @@
     </row>
     <row r="86" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A86" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B86" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F86"/>
       <c r="G86"/>
@@ -13841,10 +13883,10 @@
     </row>
     <row r="87" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A87" s="19" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B87" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F87"/>
       <c r="G87"/>
@@ -13986,10 +14028,10 @@
     </row>
     <row r="88" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A88" s="19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B88" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F88"/>
       <c r="G88"/>
@@ -14131,10 +14173,10 @@
     </row>
     <row r="89" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A89" s="19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B89" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F89"/>
       <c r="G89"/>
@@ -14276,10 +14318,10 @@
     </row>
     <row r="90" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A90" s="19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B90" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F90"/>
       <c r="G90"/>
@@ -14421,10 +14463,10 @@
     </row>
     <row r="91" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A91" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B91" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F91"/>
       <c r="G91"/>
@@ -14566,10 +14608,10 @@
     </row>
     <row r="92" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A92" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B92" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F92"/>
       <c r="G92"/>
@@ -14711,10 +14753,10 @@
     </row>
     <row r="93" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A93" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F93"/>
       <c r="G93"/>
@@ -14856,10 +14898,10 @@
     </row>
     <row r="94" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A94" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B94" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F94"/>
       <c r="G94"/>
@@ -15001,10 +15043,10 @@
     </row>
     <row r="95" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A95" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B95" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F95"/>
       <c r="G95"/>
@@ -15146,10 +15188,10 @@
     </row>
     <row r="96" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A96" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B96" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F96"/>
       <c r="G96"/>
@@ -15291,10 +15333,10 @@
     </row>
     <row r="97" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A97" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B97" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F97"/>
       <c r="G97"/>
@@ -15436,10 +15478,10 @@
     </row>
     <row r="98" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A98" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B98" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F98"/>
       <c r="G98"/>
@@ -15581,10 +15623,10 @@
     </row>
     <row r="99" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A99" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B99" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F99"/>
       <c r="G99"/>
@@ -15726,10 +15768,10 @@
     </row>
     <row r="100" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A100" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B100" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F100"/>
       <c r="G100"/>
@@ -15871,10 +15913,10 @@
     </row>
     <row r="101" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A101" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B101" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F101"/>
       <c r="G101"/>
@@ -16016,10 +16058,10 @@
     </row>
     <row r="102" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A102" s="19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B102" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F102"/>
       <c r="G102"/>
@@ -16161,10 +16203,10 @@
     </row>
     <row r="103" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A103" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B103" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F103"/>
       <c r="G103"/>
@@ -16306,10 +16348,10 @@
     </row>
     <row r="104" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A104" s="19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B104" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F104"/>
       <c r="G104"/>
@@ -16451,10 +16493,10 @@
     </row>
     <row r="105" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A105" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B105" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F105"/>
       <c r="G105"/>
@@ -16596,10 +16638,10 @@
     </row>
     <row r="106" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A106" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B106" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F106"/>
       <c r="G106"/>
@@ -16741,10 +16783,10 @@
     </row>
     <row r="107" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A107" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B107" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F107"/>
       <c r="G107"/>
@@ -16886,10 +16928,10 @@
     </row>
     <row r="108" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A108" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B108" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F108"/>
       <c r="G108"/>
@@ -17031,10 +17073,10 @@
     </row>
     <row r="109" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A109" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B109" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F109"/>
       <c r="G109"/>
@@ -17176,10 +17218,10 @@
     </row>
     <row r="110" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A110" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B110" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F110"/>
       <c r="G110"/>
@@ -17321,10 +17363,10 @@
     </row>
     <row r="111" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A111" s="27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B111" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F111"/>
       <c r="G111"/>
@@ -17466,10 +17508,10 @@
     </row>
     <row r="112" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A112" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B112" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F112"/>
       <c r="G112"/>
@@ -17611,10 +17653,10 @@
     </row>
     <row r="113" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A113" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B113" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F113"/>
       <c r="G113"/>
@@ -17756,10 +17798,10 @@
     </row>
     <row r="114" spans="1:142" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A114" s="19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B114" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F114"/>
       <c r="G114"/>
@@ -17901,115 +17943,115 @@
     </row>
     <row r="115" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A115" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B115" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="116" spans="1:142" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="81" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B116" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="117" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A117" s="81" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B117" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="118" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A118" s="19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B118" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="119" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A119" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B119" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C119" s="73"/>
     </row>
     <row r="120" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A120" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B120" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="121" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A121" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B121" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="122" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A122" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B122" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="123" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A123" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B123" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="124" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A124" s="27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B124" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="125" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A125" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B125" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A126" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B126" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="127" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A127" s="19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B127" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="128" spans="1:142" x14ac:dyDescent="0.45">
       <c r="A128" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B128" s="86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C128" s="57"/>
       <c r="D128" s="21"/>
@@ -18018,41 +18060,41 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A129" s="27" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B129" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E129" s="21"/>
       <c r="F129" s="6"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A130" s="27" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B130" s="87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A131" s="19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B131" s="86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A132" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B132" s="88" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A133" s="27" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B133" s="87" t="s">
         <v>0</v>
@@ -18060,10 +18102,10 @@
     </row>
     <row r="134" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A134" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B134" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="6"/>
@@ -18071,10 +18113,10 @@
     </row>
     <row r="135" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A135" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B135" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C135" s="6"/>
       <c r="D135" s="6"/>
@@ -18082,10 +18124,10 @@
     </row>
     <row r="136" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A136" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B136" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="6"/>
@@ -18093,10 +18135,10 @@
     </row>
     <row r="137" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A137" s="19" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B137" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C137" s="6"/>
       <c r="D137" s="6"/>
@@ -18104,10 +18146,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A138" s="19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B138" s="82" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C138" s="21"/>
       <c r="D138" s="21"/>
@@ -18115,42 +18157,42 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A139" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B139" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A140" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B140" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A141" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B141" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A142" s="19" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="143" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A143" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
@@ -18158,29 +18200,29 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A144" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C144" s="21"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C145" s="21"/>
       <c r="E145" s="21"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C146" s="21"/>
       <c r="D146" s="21"/>
@@ -18188,10 +18230,10 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C147" s="21"/>
       <c r="D147" s="21"/>
@@ -18199,18 +18241,18 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A149" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C149" s="6"/>
       <c r="D149" s="6"/>
@@ -18218,10 +18260,10 @@
     </row>
     <row r="150" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A150" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="6"/>
@@ -18229,10 +18271,10 @@
     </row>
     <row r="151" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A151" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C151" s="6"/>
       <c r="D151" s="6"/>
@@ -18240,10 +18282,10 @@
     </row>
     <row r="152" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A152" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
@@ -18251,58 +18293,58 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A159" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C159" s="6"/>
       <c r="D159" s="6"/>
@@ -18310,34 +18352,34 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="163" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A163" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C163" s="6"/>
       <c r="D163" s="6"/>
@@ -18345,10 +18387,10 @@
     </row>
     <row r="164" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A164" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B164" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="6"/>
@@ -18356,10 +18398,10 @@
     </row>
     <row r="165" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A165" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C165" s="6"/>
       <c r="D165" s="6"/>
@@ -18367,10 +18409,10 @@
     </row>
     <row r="166" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A166" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="6"/>
@@ -18378,18 +18420,18 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" s="19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A168" s="19" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="6"/>
@@ -18397,10 +18439,10 @@
     </row>
     <row r="169" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A169" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C169" s="6"/>
       <c r="D169" s="6"/>
@@ -18408,34 +18450,34 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" s="19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C173" s="21"/>
       <c r="D173" s="21"/>
@@ -18443,35 +18485,35 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B175" s="82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E175" s="21"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" s="19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="177" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A177" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C177" s="6"/>
       <c r="D177" s="6"/>
@@ -18479,10 +18521,10 @@
     </row>
     <row r="178" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A178" s="19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="6"/>
@@ -18490,10 +18532,10 @@
     </row>
     <row r="179" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A179" s="27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B179" s="42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C179" s="6"/>
       <c r="D179" s="6"/>
@@ -18501,10 +18543,10 @@
     </row>
     <row r="180" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A180" s="27" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B180" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="6"/>
@@ -18512,10 +18554,10 @@
     </row>
     <row r="181" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A181" s="19" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C181" s="6"/>
       <c r="D181" s="6"/>
@@ -18523,10 +18565,10 @@
     </row>
     <row r="182" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A182" s="19" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B182" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="6"/>
@@ -18534,7 +18576,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B183" s="17" t="s">
         <v>0</v>
@@ -18542,7 +18584,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B184" s="17" t="s">
         <v>0</v>
@@ -18550,7 +18592,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B185" s="17" t="s">
         <v>0</v>
@@ -18558,7 +18600,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" s="19" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B186" s="17" t="s">
         <v>0</v>
@@ -18566,7 +18608,7 @@
     </row>
     <row r="187" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A187" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B187" s="17" t="s">
         <v>0</v>
@@ -18577,7 +18619,7 @@
     </row>
     <row r="188" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A188" s="19" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B188" s="17" t="s">
         <v>0</v>
@@ -18588,7 +18630,7 @@
     </row>
     <row r="189" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A189" s="19" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B189" s="17" t="s">
         <v>0</v>
@@ -18599,7 +18641,7 @@
     </row>
     <row r="190" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A190" s="19" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B190" s="17" t="s">
         <v>0</v>
@@ -18610,7 +18652,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B191" s="17" t="s">
         <v>0</v>
@@ -18621,7 +18663,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192" s="19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B192" s="17" t="s">
         <v>0</v>
@@ -18629,7 +18671,7 @@
     </row>
     <row r="193" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A193" s="19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B193" s="17" t="s">
         <v>0</v>
@@ -18640,7 +18682,7 @@
     </row>
     <row r="194" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A194" s="19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B194" s="17" t="s">
         <v>0</v>
@@ -18651,7 +18693,7 @@
     </row>
     <row r="195" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A195" s="19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B195" s="17" t="s">
         <v>0</v>
@@ -18662,7 +18704,7 @@
     </row>
     <row r="196" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A196" s="19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B196" s="17" t="s">
         <v>0</v>
@@ -18673,7 +18715,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="19" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B197" s="17" t="s">
         <v>0</v>
@@ -18681,7 +18723,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" s="19" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B198" s="17" t="s">
         <v>0</v>
@@ -18689,7 +18731,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="19" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B199" s="17" t="s">
         <v>0</v>
@@ -18697,7 +18739,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" s="19" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B200" s="17" t="s">
         <v>0</v>
@@ -18866,7 +18908,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B218" s="17">
         <f>COUNTIF($B$2:$B$217,"A")</f>
@@ -18903,7 +18945,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B219" s="17">
         <f>COUNTIF($B$2:$B$217,"AA")</f>
@@ -18940,7 +18982,7 @@
     </row>
     <row r="220" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A220" s="39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B220" s="37">
         <f>COUNTIF($B$2:$B$217,"AAA")</f>
@@ -18977,7 +19019,7 @@
     </row>
     <row r="221" spans="1:9" s="33" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B221" s="42">
         <f>COUNTIF($B$2:$B$217,"shall")</f>
@@ -19014,7 +19056,7 @@
     </row>
     <row r="222" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A222" s="48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B222" s="46">
         <f>COUNTIF($B$2:$B$217,"should")</f>
@@ -19119,7 +19161,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B214">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19140,13 +19182,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B1" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="55" t="s">
         <v>234</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -19154,7 +19196,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -19162,7 +19204,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -19170,7 +19212,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -19178,10 +19220,10 @@
         <v>-1</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -19189,42 +19231,42 @@
         <v>-2</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="54" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -19246,22 +19288,22 @@
   <sheetData>
     <row r="1" spans="1:1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
